--- a/filer/12863233_hydrema.xlsx
+++ b/filer/12863233_hydrema.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/12863233_hydrema.xlsx
+++ b/filer/12863233_hydrema.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_12863233" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_12863233" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_12863233" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_12863233" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -204,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,35 +1532,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -3009,35 +3010,35 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
@@ -4391,19 +4392,19 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
@@ -4509,19 +4510,19 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
@@ -4818,6 +4819,148 @@
       </c>
       <c r="F99" s="13">
         <f>IFERROR($F$36/($F$61+$F$68)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw_12863233'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw_12863233'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw_12863233'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw_12863233'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw_12863233'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B103" s="17">
+        <f>'pengestrom_raw_12863233'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C103" s="17">
+        <f>'pengestrom_raw_12863233'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D103" s="17">
+        <f>'pengestrom_raw_12863233'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E103" s="17">
+        <f>'pengestrom_raw_12863233'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F103" s="17">
+        <f>'pengestrom_raw_12863233'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B104" s="17">
+        <f>'pengestrom_raw_12863233'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C104" s="17">
+        <f>'pengestrom_raw_12863233'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D104" s="17">
+        <f>'pengestrom_raw_12863233'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E104" s="17">
+        <f>'pengestrom_raw_12863233'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F104" s="17">
+        <f>'pengestrom_raw_12863233'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B105" s="17">
+        <f>'pengestrom_raw_12863233'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C105" s="17">
+        <f>'pengestrom_raw_12863233'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D105" s="17">
+        <f>'pengestrom_raw_12863233'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E105" s="17">
+        <f>'pengestrom_raw_12863233'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F105" s="17">
+        <f>'pengestrom_raw_12863233'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B106">
+        <f>IF(ABS(('pengestrom_raw_12863233'!$B$2+'pengestrom_raw_12863233'!$B$3+'pengestrom_raw_12863233'!$B$4)-'pengestrom_raw_12863233'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_12863233'!$B$2+'pengestrom_raw_12863233'!$B$3+'pengestrom_raw_12863233'!$B$4)-'pengestrom_raw_12863233'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C106">
+        <f>IF(ABS(('pengestrom_raw_12863233'!$C$2+'pengestrom_raw_12863233'!$C$3+'pengestrom_raw_12863233'!$C$4)-'pengestrom_raw_12863233'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_12863233'!$C$2+'pengestrom_raw_12863233'!$C$3+'pengestrom_raw_12863233'!$C$4)-'pengestrom_raw_12863233'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D106">
+        <f>IF(ABS(('pengestrom_raw_12863233'!$D$2+'pengestrom_raw_12863233'!$D$3+'pengestrom_raw_12863233'!$D$4)-'pengestrom_raw_12863233'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_12863233'!$D$2+'pengestrom_raw_12863233'!$D$3+'pengestrom_raw_12863233'!$D$4)-'pengestrom_raw_12863233'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E106">
+        <f>IF(ABS(('pengestrom_raw_12863233'!$E$2+'pengestrom_raw_12863233'!$E$3+'pengestrom_raw_12863233'!$E$4)-'pengestrom_raw_12863233'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_12863233'!$E$2+'pengestrom_raw_12863233'!$E$3+'pengestrom_raw_12863233'!$E$4)-'pengestrom_raw_12863233'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F106">
+        <f>IF(ABS(('pengestrom_raw_12863233'!$F$2+'pengestrom_raw_12863233'!$F$3+'pengestrom_raw_12863233'!$F$4)-'pengestrom_raw_12863233'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_12863233'!$F$2+'pengestrom_raw_12863233'!$F$3+'pengestrom_raw_12863233'!$F$4)-'pengestrom_raw_12863233'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4850,412 +4993,412 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>823464</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>1032932</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>1137333</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>1266482</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>1348808</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>1378993</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>10382</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>7057</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>8983</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>9389</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>12173</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>11224</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>83739</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>5065</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>-59250</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>-76420</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>-112858</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>90254</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>55449</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>60438</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>78248</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>88568</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>89729</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>96020</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>268902</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>333256</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>368402</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>392214</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>450701</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>504090</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>201990</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>221176</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>247083</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>270641</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>297134</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>302572</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>17834</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>15944</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>16234</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>18311</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>20456</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>29505</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>645</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>62</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>1215</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>48433</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>96130</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>105022</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>103261</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>131897</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>172013</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>800</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>2354</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>827</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>1411</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>1649</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>1993</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>4648</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>2059</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>12337</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>23631</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>17307</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>16519</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>44546</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>96385</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>95026</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>81025</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>116239</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>157486</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>9759</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>21338</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>20127</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>19736</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>25946</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>34226</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>34788</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>75047</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>74899</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>61289</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>90293</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>123261</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>453</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>456</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>477</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>513</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>533</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>524</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>17253</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>13265</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>32431</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>21829</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>51486</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>46020</v>
       </c>
     </row>
   </sheetData>
@@ -5287,1151 +5430,1151 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Udviklingsprojekter</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>6513</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>5759</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>5007</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>12657</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>12655</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>3818</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Patenter, varemærker mv.</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Immaterielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>6513</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>6100</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>8429</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>12657</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>12655</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>3818</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>30921</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>45165</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>44881</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>41818</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>53445</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>53264</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>24048</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>19768</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>18458</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>28150</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>37607</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>54566</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>32392</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>31893</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>29881</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>45238</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>47753</v>
       </c>
+      <c r="F8" s="17" t="n">
+        <v>57246</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="16" t="n"/>
-      <c r="D9" s="16" t="n"/>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>9796</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>19746</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>565</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>9259</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>6737</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>97157</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>96825</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>112966</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>115772</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>148064</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>171813</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
+        <v>626</v>
+      </c>
+      <c r="F13" s="17" t="n">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>1308</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>2821</v>
+      </c>
+      <c r="D14" s="17" t="n">
         <v>600</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>626</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Finansielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
-        <v>1350</v>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>1308</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>2821</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>600</v>
-      </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <v>626</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>105019</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>104233</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>124215</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>129028</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>161345</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>176258</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>3333</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>8220</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>11912</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>7310</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>4327</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>5119</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>25722</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>30060</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>37504</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>40905</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>37246</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>38628</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>300220</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>290745</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>342572</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>415669</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>532333</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>444072</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>329502</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>330398</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>394092</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>464769</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>575490</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>488245</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>82639</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>126455</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>153502</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>163213</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>194822</v>
       </c>
+      <c r="F20" s="17" t="n">
+        <v>110639</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B21" s="17" t="n">
+        <v>19248</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>11049</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>21606</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>7855</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>115230</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Andre tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>5136</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>6352</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>6114</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>2760</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>5253</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>3489</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>3696</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>3724</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>3682</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>4546</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>Udskudt skatteaktiv</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristede skattetilgodehavender</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>2152</v>
+      </c>
+      <c r="C26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="16" t="n">
-        <v>19248</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>11049</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>21606</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>7855</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>6226</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>5136</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>6352</v>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>6114</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>2760</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>1269</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>3489</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>3696</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>3724</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>3682</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>Udskudt skatteaktiv</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="n"/>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristede skattetilgodehavender</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="16" t="n">
-        <v>2152</v>
-      </c>
-      <c r="D26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="F26" s="17" t="n">
+        <v>8783</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Tilgodehavender</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>156480</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>175186</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>195038</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>209640</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>244451</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>51735</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>103237</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>50691</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>66111</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>122841</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>538613</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>672515</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>710499</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>851242</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>855536</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>Aktiver</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>642846</v>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>796730</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>839528</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>1012587</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>1031794</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for udviklingsomkostninger</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="C35" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="D35" s="17" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>90134</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>156480</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>175186</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>195038</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>209640</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>Værdipapirer</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="n"/>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Likvide beholdninger</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n">
-        <v>54764</v>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>51735</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>103237</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>50691</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>66111</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>474400</v>
-      </c>
-      <c r="C30" s="16" t="n">
-        <v>538613</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>672515</v>
-      </c>
-      <c r="E30" s="16" t="n">
-        <v>710499</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>851242</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="n">
-        <v>579419</v>
-      </c>
-      <c r="C31" s="16" t="n">
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>Andre reserver</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>Overført resultat</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>305026</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>279925</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>341214</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>431507</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>804767</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>465358</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>386264</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>345335</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>439291</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>805267</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Hensættelse til udskudt skat</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>11198</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>13474</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>11237</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>1593</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>8081</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>17358</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>20501</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>21642</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>12943</v>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>20817</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>20723</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>18839</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>16993</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>15119</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>13245</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (langfristet)</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n">
+        <v>6106</v>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>9403</v>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>11161</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>14095</v>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>10197</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (langfristet)</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>4238</v>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>126000</v>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>202000</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>184116</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>8245</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>33837</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>161992</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>237205</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>223937</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>50138</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>10244</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>24923</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>34239</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>37174</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>19120</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>Kreditinstitutter</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>55289</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>8797</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>60397</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Leasingforpligtelser (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>Leverandører af varer og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>64258</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>97961</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>103440</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>65150</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>65778</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n">
+        <v>228</v>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>6730</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>30824</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>52653</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>Selskabsskat</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>4845</v>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>7909</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>29703</v>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="17" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>47604</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>32174</v>
+      </c>
+      <c r="D55" s="17" t="n">
+        <v>42769</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>57636</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>43910</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="n">
+        <v>3959</v>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>6053</v>
+      </c>
+      <c r="D56" s="17" t="n">
+        <v>7367</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>7797</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>23624</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
+        <is>
+          <t>Kortfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="n">
+        <v>126292</v>
+      </c>
+      <c r="C57" s="17" t="n">
+        <v>227975</v>
+      </c>
+      <c r="D57" s="17" t="n">
+        <v>235345</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>336415</v>
+      </c>
+      <c r="F57" s="17" t="n">
+        <v>155573</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
+        <is>
+          <t>Gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="n">
+        <v>160130</v>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>389966</v>
+      </c>
+      <c r="D58" s="17" t="n">
+        <v>472550</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>560352</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>205710</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
+        <is>
+          <t>Passiver</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="n">
         <v>642846</v>
       </c>
-      <c r="D31" s="16" t="n">
+      <c r="C59" s="17" t="n">
         <v>796730</v>
       </c>
-      <c r="E31" s="16" t="n">
+      <c r="D59" s="17" t="n">
         <v>839528</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="E59" s="17" t="n">
         <v>1012587</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B32" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C32" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D32" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E32" s="16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>Reserve for sikringstransaktioner</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>570</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="16" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>Andre reserver</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="n"/>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>Overført resultat</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n">
-        <v>379979</v>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>305026</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>279925</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>341214</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>431507</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n">
-        <v>386414</v>
-      </c>
-      <c r="C38" s="16" t="n">
-        <v>465358</v>
-      </c>
-      <c r="D38" s="16" t="n">
-        <v>386264</v>
-      </c>
-      <c r="E38" s="16" t="n">
-        <v>345335</v>
-      </c>
-      <c r="F38" s="16" t="n">
-        <v>439291</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Hensættelse til udskudt skat</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n">
-        <v>9360</v>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>11198</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>13474</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>11237</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B40" s="16" t="n">
-        <v>15622</v>
-      </c>
-      <c r="C40" s="16" t="n">
-        <v>17358</v>
-      </c>
-      <c r="D40" s="16" t="n">
-        <v>20501</v>
-      </c>
-      <c r="E40" s="16" t="n">
-        <v>21642</v>
-      </c>
-      <c r="F40" s="16" t="n">
-        <v>12943</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
-        <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n">
-        <v>35113</v>
-      </c>
-      <c r="C42" s="16" t="n">
-        <v>20723</v>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>18839</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>16993</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>15119</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n">
-        <v>7629</v>
-      </c>
-      <c r="C43" s="16" t="n">
-        <v>6106</v>
-      </c>
-      <c r="D43" s="16" t="n">
-        <v>9403</v>
-      </c>
-      <c r="E43" s="16" t="n">
-        <v>11161</v>
-      </c>
-      <c r="F43" s="16" t="n">
-        <v>14095</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (langfristet)</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>17063</v>
-      </c>
-      <c r="C44" s="16" t="n">
-        <v>4238</v>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>126000</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>202000</v>
-      </c>
-      <c r="F44" s="16" t="n">
-        <v>184116</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n">
-        <v>63054</v>
-      </c>
-      <c r="C45" s="16" t="n">
-        <v>33837</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>161992</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>237205</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>223937</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n">
-        <v>13178</v>
-      </c>
-      <c r="C47" s="16" t="n">
-        <v>10244</v>
-      </c>
-      <c r="D47" s="16" t="n">
-        <v>24923</v>
-      </c>
-      <c r="E47" s="16" t="n">
-        <v>34239</v>
-      </c>
-      <c r="F47" s="16" t="n">
-        <v>37174</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B48" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="C48" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="16" t="n">
-        <v>55289</v>
-      </c>
-      <c r="E48" s="16" t="n">
-        <v>8797</v>
-      </c>
-      <c r="F48" s="16" t="n">
-        <v>60397</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B50" s="16" t="n">
-        <v>48292</v>
-      </c>
-      <c r="C50" s="16" t="n">
-        <v>64258</v>
-      </c>
-      <c r="D50" s="16" t="n">
-        <v>97961</v>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>103440</v>
-      </c>
-      <c r="F50" s="16" t="n">
-        <v>65150</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B51" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="16" t="n">
-        <v>228</v>
-      </c>
-      <c r="D51" s="16" t="n">
-        <v>6730</v>
-      </c>
-      <c r="E51" s="16" t="n">
-        <v>30824</v>
-      </c>
-      <c r="F51" s="16" t="n">
-        <v>52653</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
-        </is>
-      </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
-        <is>
-          <t>Selskabsskat</t>
-        </is>
-      </c>
-      <c r="B53" s="16" t="n">
-        <v>3469</v>
-      </c>
-      <c r="C53" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="16" t="n">
-        <v>4845</v>
-      </c>
-      <c r="E53" s="16" t="n">
-        <v>7909</v>
-      </c>
-      <c r="F53" s="16" t="n">
-        <v>29703</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="inlineStr">
-        <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
-        </is>
-      </c>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>Anden gæld (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B55" s="16" t="n">
-        <v>46279</v>
-      </c>
-      <c r="C55" s="16" t="n">
-        <v>47604</v>
-      </c>
-      <c r="D55" s="16" t="n">
-        <v>32174</v>
-      </c>
-      <c r="E55" s="16" t="n">
-        <v>42769</v>
-      </c>
-      <c r="F55" s="16" t="n">
-        <v>57636</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="inlineStr">
-        <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
-        </is>
-      </c>
-      <c r="B56" s="16" t="n">
-        <v>3095</v>
-      </c>
-      <c r="C56" s="16" t="n">
-        <v>3959</v>
-      </c>
-      <c r="D56" s="16" t="n">
-        <v>6053</v>
-      </c>
-      <c r="E56" s="16" t="n">
-        <v>7367</v>
-      </c>
-      <c r="F56" s="16" t="n">
-        <v>7797</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>Kortfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B57" s="16" t="n">
-        <v>114329</v>
-      </c>
-      <c r="C57" s="16" t="n">
-        <v>126292</v>
-      </c>
-      <c r="D57" s="16" t="n">
-        <v>227975</v>
-      </c>
-      <c r="E57" s="16" t="n">
-        <v>235345</v>
-      </c>
-      <c r="F57" s="16" t="n">
-        <v>336415</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>Gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B58" s="16" t="n">
-        <v>177383</v>
-      </c>
-      <c r="C58" s="16" t="n">
-        <v>160130</v>
-      </c>
-      <c r="D58" s="16" t="n">
-        <v>389966</v>
-      </c>
-      <c r="E58" s="16" t="n">
-        <v>472550</v>
-      </c>
-      <c r="F58" s="16" t="n">
-        <v>560352</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
-        <is>
-          <t>Passiver</t>
-        </is>
-      </c>
-      <c r="B59" s="16" t="n">
-        <v>579419</v>
-      </c>
-      <c r="C59" s="16" t="n">
-        <v>642846</v>
-      </c>
-      <c r="D59" s="16" t="n">
-        <v>796730</v>
-      </c>
-      <c r="E59" s="16" t="n">
-        <v>839528</v>
-      </c>
-      <c r="F59" s="16" t="n">
-        <v>1012587</v>
+      <c r="F59" s="17" t="n">
+        <v>1031794</v>
       </c>
     </row>
   </sheetData>
@@ -6440,6 +6583,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>29232</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>39037</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>33340</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>30753</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>114903</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-12948</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-27250</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-15980</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-36564</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-38869</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-19296</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>39714</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-69906</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>21231</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-19304</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6470,13 +6735,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -7190,7 +7455,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7308,7 +7573,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7484,7 +7749,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7662,13 +7927,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7707,27 +7972,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7744,28 +8009,20 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>fsa:ExchangeRateAdjustmentsOtherFinanceExpenses</t>
+          <t>fsa:CashCapitalIncrease</t>
         </is>
       </c>
       <c r="C3" s="34" t="inlineStr">
         <is>
-          <t>fsa:ExchangeRateAdjustmentsOtherFinanceExpenses</t>
-        </is>
-      </c>
-      <c r="D3" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="35" t="n">
-        <v>8765</v>
-      </c>
-      <c r="G3" s="35" t="n">
-        <v>8224</v>
-      </c>
+          <t>fsa:CashCapitalIncrease</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="n"/>
+      <c r="E3" s="35" t="n"/>
+      <c r="F3" s="35" t="n"/>
+      <c r="G3" s="35" t="n"/>
       <c r="H3" s="35" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="I3" s="36" t="inlineStr">
         <is>
@@ -7781,24 +8038,28 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>fsa:GainsLossesFromCurrentValueAdjustmentsOfFinancialInstrumentsFinanceExpenses</t>
+          <t>fsa:ExchangeRateAdjustmentsOtherFinanceExpenses</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>fsa:GainsLossesFromCurrentValueAdjustmentsOfFinancialInstrumentsFinanceExpenses</t>
-        </is>
-      </c>
-      <c r="D4" s="38" t="n"/>
-      <c r="E4" s="38" t="n"/>
+          <t>fsa:ExchangeRateAdjustmentsOtherFinanceExpenses</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="38" t="n">
+        <v>8765</v>
+      </c>
       <c r="F4" s="38" t="n">
+        <v>8224</v>
+      </c>
+      <c r="G4" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="38" t="n">
-        <v>346</v>
-      </c>
       <c r="H4" s="38" t="n">
-        <v>242</v>
+        <v>7744</v>
       </c>
       <c r="I4" s="39" t="inlineStr">
         <is>
@@ -7814,12 +8075,12 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
-          <t>fsa:GainsLossesFromCurrentValueAdjustmentsOfFinancialInstrumentsFinanceIncome</t>
+          <t>fsa:GainsLossesFromCurrentValueAdjustmentsOfFinancialInstrumentsFinanceExpenses</t>
         </is>
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>fsa:GainsLossesFromCurrentValueAdjustmentsOfFinancialInstrumentsFinanceIncome</t>
+          <t>fsa:GainsLossesFromCurrentValueAdjustmentsOfFinancialInstrumentsFinanceExpenses</t>
         </is>
       </c>
       <c r="D5" s="35" t="n"/>
@@ -7827,12 +8088,14 @@
         <v>0</v>
       </c>
       <c r="F5" s="35" t="n">
-        <v>571</v>
+        <v>346</v>
       </c>
       <c r="G5" s="35" t="n">
+        <v>242</v>
+      </c>
+      <c r="H5" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="35" t="n"/>
       <c r="I5" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7847,28 +8110,26 @@
       </c>
       <c r="B6" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermDeferredIncome</t>
+          <t>fsa:GainsLossesFromCurrentValueAdjustmentsOfFinancialInstrumentsFinanceIncome</t>
         </is>
       </c>
       <c r="C6" s="37" t="inlineStr">
         <is>
-          <t>fsa:LongtermDeferredIncome</t>
+          <t>fsa:GainsLossesFromCurrentValueAdjustmentsOfFinancialInstrumentsFinanceIncome</t>
         </is>
       </c>
       <c r="D6" s="38" t="n">
-        <v>2249</v>
+        <v>0</v>
       </c>
       <c r="E6" s="38" t="n">
-        <v>1771</v>
+        <v>571</v>
       </c>
       <c r="F6" s="38" t="n">
-        <v>1716</v>
-      </c>
-      <c r="G6" s="38" t="n">
-        <v>1180</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G6" s="38" t="n"/>
       <c r="H6" s="38" t="n">
-        <v>2242</v>
+        <v>447</v>
       </c>
       <c r="I6" s="39" t="inlineStr">
         <is>
@@ -7884,27 +8145,29 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermPayablesToAssociates</t>
+          <t>fsa:LongtermDeferredIncome</t>
         </is>
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>fsa:LongtermPayablesToAssociates</t>
+          <t>fsa:LongtermDeferredIncome</t>
         </is>
       </c>
       <c r="D7" s="35" t="n">
-        <v>1000</v>
+        <v>1771</v>
       </c>
       <c r="E7" s="35" t="n">
-        <v>1000</v>
+        <v>1716</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>1000</v>
+        <v>1180</v>
       </c>
       <c r="G7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="35" t="n"/>
+        <v>2242</v>
+      </c>
+      <c r="H7" s="35" t="n">
+        <v>6589</v>
+      </c>
       <c r="I7" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7919,17 +8182,23 @@
       </c>
       <c r="B8" s="37" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfLongtermDebt</t>
+          <t>fsa:LongtermPayablesToAssociates</t>
         </is>
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>fsa:RaisingOfLongtermDebt</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n"/>
-      <c r="E8" s="38" t="n"/>
-      <c r="F8" s="38" t="n"/>
+          <t>fsa:LongtermPayablesToAssociates</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F8" s="38" t="n">
+        <v>0</v>
+      </c>
       <c r="G8" s="38" t="n"/>
       <c r="H8" s="38" t="n"/>
       <c r="I8" s="39" t="inlineStr">
@@ -7946,29 +8215,19 @@
       </c>
       <c r="B9" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReductionOfLeaseCommitments</t>
+          <t>fsa:RaisingOfLongtermDebt</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>fsa:ReductionOfLeaseCommitments</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>-603</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>-3864</v>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>-3691</v>
-      </c>
-      <c r="G9" s="35" t="n">
-        <v>-6571</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>-2895</v>
-      </c>
+          <t>fsa:RaisingOfLongtermDebt</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n"/>
+      <c r="E9" s="35" t="n"/>
+      <c r="F9" s="35" t="n"/>
+      <c r="G9" s="35" t="n"/>
+      <c r="H9" s="35" t="n"/>
       <c r="I9" s="36" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7983,28 +8242,28 @@
       </c>
       <c r="B10" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:ReductionOfLeaseCommitments</t>
         </is>
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:ReductionOfLeaseCommitments</t>
         </is>
       </c>
       <c r="D10" s="38" t="n">
-        <v>-3565</v>
+        <v>-3864</v>
       </c>
       <c r="E10" s="38" t="n">
-        <v>332</v>
+        <v>-3691</v>
       </c>
       <c r="F10" s="38" t="n">
-        <v>-4231</v>
+        <v>-6571</v>
       </c>
       <c r="G10" s="38" t="n">
-        <v>-5879</v>
+        <v>-2895</v>
       </c>
       <c r="H10" s="38" t="n">
-        <v>-2216</v>
+        <v>-4259</v>
       </c>
       <c r="I10" s="39" t="inlineStr">
         <is>
@@ -8020,30 +8279,67 @@
       </c>
       <c r="B11" s="34" t="inlineStr">
         <is>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+        </is>
+      </c>
+      <c r="D11" s="35" t="n">
+        <v>332</v>
+      </c>
+      <c r="E11" s="35" t="n">
+        <v>-4231</v>
+      </c>
+      <c r="F11" s="35" t="n">
+        <v>-5879</v>
+      </c>
+      <c r="G11" s="35" t="n">
+        <v>-2216</v>
+      </c>
+      <c r="H11" s="35" t="n">
+        <v>-9500</v>
+      </c>
+      <c r="I11" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="inlineStr">
+        <is>
           <t>fsa:WorkPerformedByEntityAndCapitalised</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C12" s="37" t="inlineStr">
         <is>
           <t>fsa:WorkPerformedByEntityAndCapitalised</t>
         </is>
       </c>
-      <c r="D11" s="35" t="n">
-        <v>-130</v>
-      </c>
-      <c r="E11" s="35" t="n">
+      <c r="D12" s="38" t="n">
         <v>-767</v>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="E12" s="38" t="n">
         <v>-3713</v>
       </c>
-      <c r="G11" s="35" t="n">
+      <c r="F12" s="38" t="n">
         <v>-5689</v>
       </c>
-      <c r="H11" s="35" t="n">
+      <c r="G12" s="38" t="n">
         <v>-1953</v>
       </c>
-      <c r="I11" s="36" t="inlineStr">
+      <c r="H12" s="38" t="n">
+        <v>-1095</v>
+      </c>
+      <c r="I12" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
